--- a/AAII_Financials/Yearly/KPCPY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KPCPY_YR_FIN.xlsx
@@ -2241,7 +2241,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>98606300</v>
+        <v>98605600</v>
       </c>
       <c r="E60" s="3">
         <v>84431000</v>
@@ -2307,7 +2307,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>20621300</v>
+        <v>20621900</v>
       </c>
       <c r="E62" s="3">
         <v>18277000</v>
